--- a/output/pdf_financials_xlsx/DB.xlsx
+++ b/output/pdf_financials_xlsx/DB.xlsx
@@ -4065,34 +4065,34 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.493708</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.493708</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.493708</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.456</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>8.260999999999999</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>15.264</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>16.089</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>16.299</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>16.208</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>16.746</v>
       </c>
     </row>
     <row r="93">
@@ -7154,7 +7154,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -10518,7 +10522,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -12200,7 +12208,11 @@
           <t>Reserves 19</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -14252,7 +14264,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>1.493708</v>
       </c>
@@ -14650,7 +14666,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DB.xlsx
+++ b/output/pdf_financials_xlsx/DB.xlsx
@@ -1831,34 +1831,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>5.5e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000154</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.2e-05</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>11.654</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.919</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.966</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.481</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>6.997</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>7.494</v>
       </c>
     </row>
     <row r="35">
@@ -1905,34 +1905,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>5.5e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000154</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>5.2e-05</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>11.654</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.919</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.966</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.481</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>6.997</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>7.494</v>
       </c>
     </row>
     <row r="37">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -32458,7 +32458,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">

--- a/output/pdf_financials_xlsx/DB.xlsx
+++ b/output/pdf_financials_xlsx/DB.xlsx
@@ -4861,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -18624,7 +18624,11 @@
           <t>Proceeds on disposal of property, plant, equipment 23</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -19866,7 +19870,11 @@
           <t>Proceeds on disposal of property, plant and equipment 23</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
